--- a/astro-site/public/dl/kit-tareas-chocolateria/06-eventos-temporada.xlsx
+++ b/astro-site/public/dl/kit-tareas-chocolateria/06-eventos-temporada.xlsx
@@ -691,7 +691,7 @@
     <row r="18">
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>Versión 2.0 · agosto 2026 · aichef.pro/kit-tareas-chocolateria · info@aichef.pro</t>
+          <t>Versión 2.1 · octubre 2026 · aichef.pro/kit-tareas-chocolateria · info@aichef.pro</t>
         </is>
       </c>
     </row>
@@ -1973,7 +1973,7 @@
       </c>
       <c r="B17" s="9" t="inlineStr">
         <is>
-          <t>Envasar y etiquetar la colección de Pascua: denominación, peso neto, lote, consumo preferente y alérgenos declarados (leche, frutos secos, soja, gluten y huevo)</t>
+          <t>Envasar y etiquetar la colección de Pascua: denominación, peso neto, lote, consumo preferente y alérgenos declarados (leche, huevo, cereales con gluten, soja, cacahuetes, frutos de cáscara, sésamo y sulfitos)</t>
         </is>
       </c>
       <c r="C17" s="16" t="inlineStr">
